--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111422</v>
+        <v>111429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111429</v>
+        <v>111430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111430</v>
+        <v>111435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111435</v>
+        <v>111437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111437</v>
+        <v>111443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111443</v>
+        <v>111445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111445</v>
+        <v>111446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
